--- a/data/trans_orig/P6707-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6707-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2012</t>
+          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2012 (tasa de respuesta: 98,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36838</t>
+          <t>36439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64467</t>
+          <t>62410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60605</t>
+          <t>60376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93965</t>
+          <t>93716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>30183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63235</t>
+          <t>62643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,82 +973,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>33433</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>24307</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44119</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>21,36%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>82706</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>67154</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>100029</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>23,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>33433</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24087</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>45436</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>82706</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>68304</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>99807</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60782</t>
+          <t>60695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40188</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62138</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94719</t>
+          <t>93625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88318</t>
+          <t>89374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120056</t>
+          <t>122048</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42922</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66291</t>
+          <t>67665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139376</t>
+          <t>138179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180304</t>
+          <t>177059</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48856</t>
+          <t>48141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80342</t>
+          <t>80957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54159</t>
+          <t>54748</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84897</t>
+          <t>82701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123503</t>
+          <t>123348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>39190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>35722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39301</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66469</t>
+          <t>68153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76487</t>
+          <t>77489</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>111928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44053</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70864</t>
+          <t>71185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127996</t>
+          <t>129272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173485</t>
+          <t>172416</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>55311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67891</t>
+          <t>68587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103551</t>
+          <t>103465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146180</t>
+          <t>145607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133547</t>
+          <t>133912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175463</t>
+          <t>174830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>74873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108752</t>
+          <t>108686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218563</t>
+          <t>218935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268143</t>
+          <t>270926</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>39709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66676</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58635</t>
+          <t>58018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79579</t>
+          <t>79767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114856</t>
+          <t>116480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47280</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>24623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64835</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49726</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80293</t>
+          <t>79291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>79886</t>
+          <t>79179</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117806</t>
+          <t>117022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51865</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82419</t>
+          <t>83264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32031</t>
+          <t>31611</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56295</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89623</t>
+          <t>90447</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128079</t>
+          <t>130478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87060</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>122831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61664</t>
+          <t>62427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92405</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161351</t>
+          <t>156091</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209304</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39625</t>
+          <t>38750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68601</t>
+          <t>68647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55709</t>
+          <t>54539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84580</t>
+          <t>84399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101996</t>
+          <t>102364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142815</t>
+          <t>142915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>26726</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52610</t>
+          <t>52608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45960</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>57480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90159</t>
+          <t>91813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>92352</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128377</t>
+          <t>129923</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92210</t>
+          <t>92787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>163193</t>
+          <t>162147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>211535</t>
+          <t>208259</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>95192</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132572</t>
+          <t>132197</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45660</t>
+          <t>45460</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>72602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149267</t>
+          <t>150163</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193018</t>
+          <t>195434</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84606</t>
+          <t>84584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121722</t>
+          <t>121273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77111</t>
+          <t>78105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>141562</t>
+          <t>138038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188725</t>
+          <t>186208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>188523</t>
+          <t>189560</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245980</t>
+          <t>245674</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>154699</t>
+          <t>155532</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205990</t>
+          <t>206676</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>359110</t>
+          <t>356745</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>438019</t>
+          <t>434026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98422</t>
+          <t>97379</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142292</t>
+          <t>140796</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>70541</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105534</t>
+          <t>107729</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179261</t>
+          <t>179181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>236623</t>
+          <t>239003</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>284747</t>
+          <t>284444</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>351269</t>
+          <t>348286</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>175260</t>
+          <t>174013</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>227693</t>
+          <t>225231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>476718</t>
+          <t>473710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>557371</t>
+          <t>558148</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>264558</t>
+          <t>268120</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>329640</t>
+          <t>331276</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>159101</t>
+          <t>156992</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>210221</t>
+          <t>209602</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>446029</t>
+          <t>439405</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>529869</t>
+          <t>523109</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>425121</t>
+          <t>426379</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>498556</t>
+          <t>498400</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>257593</t>
+          <t>259338</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>315399</t>
+          <t>314762</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>699780</t>
+          <t>701916</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>792793</t>
+          <t>799461</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2016</t>
+          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>55147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>49252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67060</t>
+          <t>66773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98693</t>
+          <t>97186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27129</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49024</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33984</t>
+          <t>34523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47250</t>
+          <t>46799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74965</t>
+          <t>77227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42797</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>68238</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54601</t>
+          <t>53276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>80884</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114593</t>
+          <t>114034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>42539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>68228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>42220</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72123</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105361</t>
+          <t>102363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41778</t>
+          <t>41699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67969</t>
+          <t>68742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>41637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69203</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103110</t>
+          <t>102285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>54829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85504</t>
+          <t>84921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>68906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102892</t>
+          <t>101681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143918</t>
+          <t>142917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>54761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87601</t>
+          <t>87007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51352</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>89935</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127462</t>
+          <t>128638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91752</t>
+          <t>91135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130439</t>
+          <t>128490</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62538</t>
+          <t>61235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91553</t>
+          <t>90411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>164081</t>
+          <t>162472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>210497</t>
+          <t>209583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62647</t>
+          <t>63057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96777</t>
+          <t>95535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116848</t>
+          <t>115508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>158247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>72419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106334</t>
+          <t>107284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63556</t>
+          <t>62733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116454</t>
+          <t>115184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158172</t>
+          <t>158248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61171</t>
+          <t>61390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27338</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50204</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93994</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133939</t>
+          <t>134932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42542</t>
+          <t>44606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72926</t>
+          <t>72932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59809</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84541</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124103</t>
+          <t>123213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99085</t>
+          <t>97448</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136698</t>
+          <t>135571</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64129</t>
+          <t>64068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92679</t>
+          <t>93406</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172003</t>
+          <t>172353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>218118</t>
+          <t>219257</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71756</t>
+          <t>73716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>49008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76758</t>
+          <t>78227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100479</t>
+          <t>101477</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141618</t>
+          <t>142033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70785</t>
+          <t>71437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>36080</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60595</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86131</t>
+          <t>86240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124123</t>
+          <t>123376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93095</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69837</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104093</t>
+          <t>102549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137772</t>
+          <t>134445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184015</t>
+          <t>182283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44279</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>71297</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>49343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>76007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>114178</t>
+          <t>112234</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>83347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119364</t>
+          <t>118404</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62919</t>
+          <t>62263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95134</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>154916</t>
+          <t>154764</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202420</t>
+          <t>202789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77082</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111442</t>
+          <t>111752</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>55328</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83976</t>
+          <t>84182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139679</t>
+          <t>139241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184465</t>
+          <t>185324</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>60443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91313</t>
+          <t>91787</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45739</t>
+          <t>45650</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73934</t>
+          <t>73178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112959</t>
+          <t>113918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>154876</t>
+          <t>156159</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>230908</t>
+          <t>234333</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>292223</t>
+          <t>292295</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187198</t>
+          <t>187716</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241792</t>
+          <t>241666</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>434851</t>
+          <t>433140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>513143</t>
+          <t>515759</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>194631</t>
+          <t>194618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>249012</t>
+          <t>251839</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123185</t>
+          <t>123575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>168319</t>
+          <t>167670</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>327410</t>
+          <t>332905</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>402366</t>
+          <t>404683</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>351189</t>
+          <t>348879</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>418980</t>
+          <t>420030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>246841</t>
+          <t>246705</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>300267</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>612212</t>
+          <t>608503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>697967</t>
+          <t>696578</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>256570</t>
+          <t>256008</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>318704</t>
+          <t>314462</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>194205</t>
+          <t>196577</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>246193</t>
+          <t>250355</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>466478</t>
+          <t>462761</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>551074</t>
+          <t>545298</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>242971</t>
+          <t>244228</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>305574</t>
+          <t>304800</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>163796</t>
+          <t>159770</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>213621</t>
+          <t>209883</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>416938</t>
+          <t>421507</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>494612</t>
+          <t>498887</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2023</t>
+          <t>Población según si tiene influencia sobre la cantidad de trabajo que se le asigna en 2023 (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12398</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37194</t>
+          <t>36221</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>20433</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>42501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49858</t>
+          <t>52120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60934</t>
+          <t>61290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>360052</t>
+          <t>358439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>30405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49265</t>
+          <t>48522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116655</t>
+          <t>119273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>449817</t>
+          <t>450654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47770</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61419</t>
+          <t>59231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>139075</t>
+          <t>138975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43055</t>
+          <t>43125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169068</t>
+          <t>169814</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>73141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77198</t>
+          <t>75745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98914</t>
+          <t>99217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15756</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>105231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32630</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54165</t>
+          <t>53707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44351</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49490</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20378</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37307</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27340</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54196</t>
+          <t>53997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79259</t>
+          <t>79687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>38425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>30885</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53092</t>
+          <t>52081</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27972</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>52601</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26245</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7942</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>41558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>152243</t>
+          <t>154986</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>537047</t>
+          <t>549111</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98463</t>
+          <t>98333</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>130012</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>274121</t>
+          <t>274732</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>731911</t>
+          <t>755625</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76576</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37417</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60086</t>
+          <t>60976</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45891</t>
+          <t>44586</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129735</t>
+          <t>129430</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195164</t>
+          <t>192956</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67215</t>
+          <t>67296</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93927</t>
+          <t>93899</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>98249</t>
+          <t>96640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>269200</t>
+          <t>267043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>125140</t>
+          <t>124543</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>43892</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>67608</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65477</t>
+          <t>61386</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>175380</t>
+          <t>176813</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31685</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>147270</t>
+          <t>144081</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69828</t>
+          <t>71430</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>199131</t>
+          <t>198828</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6707-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6707-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62410</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>59386</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93716</t>
+          <t>92043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30183</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>21909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>45322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37605</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62643</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44119</t>
+          <t>45879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>68420</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100029</t>
+          <t>99915</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34994</t>
+          <t>35966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60695</t>
+          <t>61654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>39348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>62033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93625</t>
+          <t>95914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89374</t>
+          <t>87874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122048</t>
+          <t>119991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43438</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67665</t>
+          <t>67793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138179</t>
+          <t>138377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177059</t>
+          <t>179398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48141</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80957</t>
+          <t>80190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54748</t>
+          <t>54657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82701</t>
+          <t>83873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123348</t>
+          <t>125479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18640</t>
+          <t>17469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35722</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39086</t>
+          <t>38252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68153</t>
+          <t>66365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>77461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111928</t>
+          <t>112055</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>43244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71185</t>
+          <t>70645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129272</t>
+          <t>126110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172416</t>
+          <t>171157</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55311</t>
+          <t>56375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88813</t>
+          <t>87586</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40393</t>
+          <t>41027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103465</t>
+          <t>104322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145607</t>
+          <t>147394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133912</t>
+          <t>132970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174830</t>
+          <t>172745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74873</t>
+          <t>74922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108686</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218935</t>
+          <t>218986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270926</t>
+          <t>270155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66468</t>
+          <t>66990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>33746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>59437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79767</t>
+          <t>78129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116480</t>
+          <t>117268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>48036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24623</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>37252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64414</t>
+          <t>66144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48919</t>
+          <t>50242</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79291</t>
+          <t>79534</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>47259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>80146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117022</t>
+          <t>117362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51186</t>
+          <t>51629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83264</t>
+          <t>81684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57396</t>
+          <t>56363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90447</t>
+          <t>89110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130478</t>
+          <t>130757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87440</t>
+          <t>87387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122831</t>
+          <t>122548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62427</t>
+          <t>63948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92053</t>
+          <t>91550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>156091</t>
+          <t>158487</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203531</t>
+          <t>205177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38750</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84399</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102364</t>
+          <t>102009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142915</t>
+          <t>145299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52608</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23873</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>57480</t>
+          <t>57941</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91813</t>
+          <t>93080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92352</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>129923</t>
+          <t>129382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60990</t>
+          <t>60703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>92076</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>162147</t>
+          <t>161687</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>208259</t>
+          <t>211593</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95192</t>
+          <t>96845</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132197</t>
+          <t>130859</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45460</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72602</t>
+          <t>70689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150163</t>
+          <t>149177</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195434</t>
+          <t>194143</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121273</t>
+          <t>120010</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47939</t>
+          <t>48114</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78105</t>
+          <t>76464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138038</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186208</t>
+          <t>186257</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189560</t>
+          <t>190643</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245674</t>
+          <t>247061</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>155532</t>
+          <t>156872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206676</t>
+          <t>209338</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>356745</t>
+          <t>361762</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>434026</t>
+          <t>433926</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97379</t>
+          <t>98068</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140796</t>
+          <t>141979</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>72360</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107729</t>
+          <t>109118</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179181</t>
+          <t>179035</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>239003</t>
+          <t>233330</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>284444</t>
+          <t>285721</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>348286</t>
+          <t>349559</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>173629</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>225231</t>
+          <t>227503</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>473710</t>
+          <t>477862</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>558148</t>
+          <t>558185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>268120</t>
+          <t>268904</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>331276</t>
+          <t>332621</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156992</t>
+          <t>158630</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>209602</t>
+          <t>207835</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>439405</t>
+          <t>433837</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>523109</t>
+          <t>519728</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>426379</t>
+          <t>425394</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>498400</t>
+          <t>500208</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>259338</t>
+          <t>256260</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>314762</t>
+          <t>314695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>701916</t>
+          <t>699983</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>799461</t>
+          <t>794516</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55147</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28668</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49252</t>
+          <t>50566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>65808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97186</t>
+          <t>97716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77227</t>
+          <t>77095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>42388</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68238</t>
+          <t>68575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53276</t>
+          <t>54367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80884</t>
+          <t>81000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114034</t>
+          <t>115266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>42564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68228</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71184</t>
+          <t>70194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102363</t>
+          <t>104404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68742</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41637</t>
+          <t>41708</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68857</t>
+          <t>69814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102285</t>
+          <t>103001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54829</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84921</t>
+          <t>84689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>42256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68906</t>
+          <t>66869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101681</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142917</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54761</t>
+          <t>54484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87007</t>
+          <t>85853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>51700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89935</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128638</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91135</t>
+          <t>92841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128490</t>
+          <t>129910</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61235</t>
+          <t>61181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>92608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162472</t>
+          <t>160226</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>209583</t>
+          <t>209218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63057</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95535</t>
+          <t>96035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>46146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>72941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115508</t>
+          <t>115901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158247</t>
+          <t>158168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72419</t>
+          <t>70867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107284</t>
+          <t>106450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35914</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62733</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115184</t>
+          <t>115832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158248</t>
+          <t>157621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61390</t>
+          <t>60053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94428</t>
+          <t>93086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27812</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50275</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>95162</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134932</t>
+          <t>133718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44606</t>
+          <t>45658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>74806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34587</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>84673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123213</t>
+          <t>122463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97448</t>
+          <t>99822</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>137720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64068</t>
+          <t>63057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93406</t>
+          <t>91718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172353</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>219257</t>
+          <t>219203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45077</t>
+          <t>43939</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49008</t>
+          <t>48296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78227</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101477</t>
+          <t>102271</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142033</t>
+          <t>144095</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43819</t>
+          <t>42433</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71437</t>
+          <t>70652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61252</t>
+          <t>61261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86240</t>
+          <t>85480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123376</t>
+          <t>122614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91738</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69784</t>
+          <t>67670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102549</t>
+          <t>100884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134445</t>
+          <t>137824</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182283</t>
+          <t>184167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71297</t>
+          <t>73071</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49343</t>
+          <t>49525</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76007</t>
+          <t>75874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112234</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83347</t>
+          <t>83711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118404</t>
+          <t>119512</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>63397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93075</t>
+          <t>94208</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>154764</t>
+          <t>154196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>202789</t>
+          <t>204709</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77596</t>
+          <t>77770</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111752</t>
+          <t>111226</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55328</t>
+          <t>54097</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84182</t>
+          <t>84156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139241</t>
+          <t>140246</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185324</t>
+          <t>184762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60443</t>
+          <t>59169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91787</t>
+          <t>91762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45650</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>73993</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113918</t>
+          <t>114393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156159</t>
+          <t>157169</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>234333</t>
+          <t>229885</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>292295</t>
+          <t>290552</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187716</t>
+          <t>188886</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241666</t>
+          <t>241697</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>433140</t>
+          <t>433886</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>515759</t>
+          <t>515646</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>194618</t>
+          <t>192846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>251839</t>
+          <t>247089</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123575</t>
+          <t>124052</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>167670</t>
+          <t>167671</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>332905</t>
+          <t>327765</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>404683</t>
+          <t>403023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>348879</t>
+          <t>348486</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>420030</t>
+          <t>413632</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>246705</t>
+          <t>245839</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>300267</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>608503</t>
+          <t>610131</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>696578</t>
+          <t>701757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>256008</t>
+          <t>254153</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>314462</t>
+          <t>320635</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,82 +7456,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>220765</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>194795</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>248217</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>505499</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>461400</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>543754</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>18,76%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>22,11%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>220765</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>196577</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>250355</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>24,14%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>505499</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>462761</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>545298</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>20,55%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>244228</t>
+          <t>243741</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>304800</t>
+          <t>303839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159770</t>
+          <t>161359</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>209883</t>
+          <t>211359</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>421507</t>
+          <t>418127</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>498887</t>
+          <t>498182</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>23497</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36221</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>32252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>42039</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>35107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59333</t>
+          <t>61285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,32 +8159,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,22 +8194,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12672</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>31123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15030</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>29307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45591</t>
+          <t>50195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>23170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>26587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>15212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>42878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>8682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>35760</t>
+          <t>40767</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>59063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>271473</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61290</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>358439</t>
+          <t>44488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>54944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>310327</t>
+          <t>75097</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119273</t>
+          <t>60428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450654</t>
+          <t>93200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46970</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,32 +8841,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8876,32 +8876,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59231</t>
+          <t>45973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>43329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138975</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34498</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26748</t>
+          <t>28583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>46057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>84002</t>
+          <t>92796</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>77277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169814</t>
+          <t>111219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>18203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73141</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37212</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75745</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99217</t>
+          <t>52980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>60057</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>46897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105231</t>
+          <t>76735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>115534</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115534</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115534</t>
+          <t>127268</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>512104</t>
+          <t>299168</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>512104</t>
+          <t>299168</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>512104</t>
+          <t>299168</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>39489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>37663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42334</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>43138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>71174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>31258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>28296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>39529</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43595</t>
+          <t>53449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>19760</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25172</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>36191</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47791</t>
+          <t>51097</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>22615</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>20617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37733</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>50825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>43834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>74936</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53997</t>
+          <t>61491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79687</t>
+          <t>88452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>20136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>14714</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27132</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>37557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>40914</t>
+          <t>40729</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30885</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52081</t>
+          <t>52723</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41886</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>31788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52601</t>
+          <t>52942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>8975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>24947</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41558</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>88423</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>88423</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>88423</t>
+          <t>97120</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196072</t>
+          <t>213897</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>196072</t>
+          <t>213897</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196072</t>
+          <t>213897</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>347828</t>
+          <t>120472</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>154986</t>
+          <t>97283</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>549111</t>
+          <t>142836</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>131737</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98333</t>
+          <t>113414</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130012</t>
+          <t>148807</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>461399</t>
+          <t>252208</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>274732</t>
+          <t>226616</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>755625</t>
+          <t>281223</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>39316</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>72883</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>47548</t>
+          <t>54124</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>67306</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>91767</t>
+          <t>106548</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44586</t>
+          <t>87798</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129430</t>
+          <t>127092</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>116886</t>
+          <t>125503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>192956</t>
+          <t>150344</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>79738</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67296</t>
+          <t>70551</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93899</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>196624</t>
+          <t>210920</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>96640</t>
+          <t>183397</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>267043</t>
+          <t>237537</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>74054</t>
+          <t>80982</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>64470</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>124543</t>
+          <t>98603</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>54524</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>128578</t>
+          <t>139613</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>61386</t>
+          <t>119720</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>176813</t>
+          <t>163489</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>87135</t>
+          <t>100583</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33511</t>
+          <t>79159</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>144081</t>
+          <t>124404</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>78488</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>145110</t>
+          <t>164376</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>71430</t>
+          <t>138582</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>198828</t>
+          <t>190776</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>353354</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>353354</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>353354</t>
+          <t>393702</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1023477</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1023477</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1023477</t>
+          <t>873666</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
